--- a/results/pr_Agency_EBCI/test/05_08 Artem/cv_scores/01_calib.xlsx
+++ b/results/pr_Agency_EBCI/test/05_08 Artem/cv_scores/01_calib.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X97"/>
+  <dimension ref="A1:X121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,35 +667,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -704,19 +704,19 @@
         <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2000000018475503</v>
+        <v>0.1000000275223826</v>
       </c>
       <c r="W3" t="n">
-        <v>6.110459374660732</v>
+        <v>3.604418235039689</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -753,29 +753,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0.6</v>
@@ -784,10 +784,10 @@
         <v>0.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -796,13 +796,13 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2844012318443402</v>
+        <v>0.2000000018475503</v>
       </c>
       <c r="W4" t="n">
-        <v>7.45969336364156</v>
+        <v>6.110459374660732</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -849,7 +849,7 @@
         <v>0.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="K5" t="n">
         <v>0.7272727272727272</v>
@@ -885,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2844012318443402</v>
       </c>
       <c r="W5" t="n">
-        <v>10.81309601673515</v>
+        <v>7.45969336364156</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -921,60 +921,60 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1291540370928153</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0.439426461592536</v>
+        <v>10.81309601673515</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1011,35 +1011,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.92</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1048,19 +1048,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1444909497389011</v>
+        <v>0.1291540370928153</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4619096499929872</v>
+        <v>0.439426461592536</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1143,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08410151277363462</v>
+        <v>0.08753827376387292</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2407127221519203</v>
+        <v>0.2489752363969794</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1183,56 +1183,56 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0.92</v>
       </c>
       <c r="K9" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09781228181572969</v>
+        <v>0.1444909497389011</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2789049219400562</v>
+        <v>0.4619096499929872</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -1265,60 +1265,60 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2959885334330952</v>
+        <v>0.08410151277363462</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8240389637060513</v>
+        <v>0.2407127221519203</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -1351,60 +1351,60 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2829126190409199</v>
+        <v>0.09781228181572969</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7652800040366147</v>
+        <v>0.2789049219400562</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -1441,56 +1441,56 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3101287215807708</v>
+        <v>0.2959885334330952</v>
       </c>
       <c r="W12" t="n">
-        <v>1.649869841060581</v>
+        <v>0.8240389637060513</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1537,7 +1537,7 @@
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.7272727272727272</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3089138389539036</v>
+        <v>0.3320741135513426</v>
       </c>
       <c r="W13" t="n">
-        <v>1.701527728764196</v>
+        <v>1.942279102465707</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -1605,43 +1605,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7499999999999999</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L14" t="n">
         <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="n">
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.4</v>
@@ -1650,19 +1650,19 @@
         <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1541812276628035</v>
+        <v>0.2829126190409199</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5229203496350867</v>
+        <v>0.7652800040366147</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -1691,37 +1691,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.24</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
         <v>0.6</v>
@@ -1730,10 +1730,10 @@
         <v>0.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -1742,13 +1742,13 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.700005954332438</v>
+        <v>0.3101287215807708</v>
       </c>
       <c r="W15" t="n">
-        <v>15.74428420578021</v>
+        <v>1.649869841060581</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -1777,15 +1777,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1795,46 +1795,46 @@
         <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.88</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1847205611701262</v>
+        <v>0.3089138389539036</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6631831593149385</v>
+        <v>1.701527728764196</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -1871,56 +1871,56 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.36</v>
+        <v>0.92</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6997140943762866</v>
+        <v>0.1541812276628035</v>
       </c>
       <c r="W17" t="n">
-        <v>12.56947578865288</v>
+        <v>0.5229203496350867</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -1953,39 +1953,39 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.64</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="L18" t="n">
         <v>0.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8</v>
       </c>
       <c r="N18" t="n">
         <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.2</v>
@@ -1994,19 +1994,19 @@
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2575666184109092</v>
+        <v>0.09435285904391397</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7623370454968554</v>
+        <v>0.2656611947354567</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2047,52 +2047,52 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3468791071338126</v>
+        <v>0.700005954332438</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9444060869598385</v>
+        <v>15.74428420578021</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2133,31 +2133,31 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="L20" t="n">
         <v>0.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N20" t="n">
         <v>0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.4</v>
@@ -2166,19 +2166,19 @@
         <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4199470364773889</v>
+        <v>0.1847205611701262</v>
       </c>
       <c r="W20" t="n">
-        <v>2.50839493222977</v>
+        <v>0.6631831593149385</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2219,52 +2219,52 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5454545454545454</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4313476613420268</v>
+        <v>0.6997140943762866</v>
       </c>
       <c r="W21" t="n">
-        <v>2.551805585642408</v>
+        <v>12.56947578865288</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4400000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="K22" t="n">
         <v>0.6666666666666666</v>
@@ -2347,10 +2347,10 @@
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3497579777777077</v>
+        <v>0.2575666184109092</v>
       </c>
       <c r="W22" t="n">
-        <v>1.152230301510467</v>
+        <v>0.7623370454968554</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -2383,33 +2383,33 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O23" t="n">
         <v>0.4</v>
@@ -2418,10 +2418,10 @@
         <v>0.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
         <v>2</v>
@@ -2430,13 +2430,13 @@
         <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3534120258352476</v>
+        <v>0.4216063226255404</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09421226265216</v>
+        <v>2.497831089150052</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -2469,39 +2469,39 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.5</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.5454545454545454</v>
-      </c>
       <c r="L24" t="n">
         <v>0.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N24" t="n">
         <v>0.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.4</v>
@@ -2510,19 +2510,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4419734148908401</v>
+        <v>0.3468791071338126</v>
       </c>
       <c r="W24" t="n">
-        <v>2.096509776949293</v>
+        <v>0.9444060869598385</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -2555,11 +2555,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2569,7 +2569,7 @@
         <v>0.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.5454545454545454</v>
@@ -2605,10 +2605,10 @@
         <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4385436849399495</v>
+        <v>0.4199470364773889</v>
       </c>
       <c r="W25" t="n">
-        <v>2.119676014710494</v>
+        <v>2.50839493222977</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -2632,69 +2632,69 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0.09999966178816919</v>
+        <v>0.4313476613420268</v>
       </c>
       <c r="W26" t="n">
-        <v>1.31164857385537</v>
+        <v>2.551805585642408</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -2718,69 +2718,69 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>0.000241311481265592</v>
+        <v>0.3497579777777077</v>
       </c>
       <c r="W27" t="n">
-        <v>0.005037504856953613</v>
+        <v>1.152230301510467</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -2804,69 +2804,69 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0.100035789431668</v>
+        <v>0.4382828504324262</v>
       </c>
       <c r="W28" t="n">
-        <v>1.813017768857535</v>
+        <v>2.246146141020459</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -2890,69 +2890,69 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.75745875047518e-11</v>
+        <v>0.3534120258352476</v>
       </c>
       <c r="W29" t="n">
-        <v>1.325823798115662e-06</v>
+        <v>1.09421226265216</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -2976,69 +2976,69 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
-        <v>0.88</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>0.1470072949078548</v>
+        <v>0.4419734148908401</v>
       </c>
       <c r="W30" t="n">
-        <v>0.43942917902641</v>
+        <v>2.096509776949293</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -3062,48 +3062,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[9.0, 13.0]</t>
+          <t>[8.0, 12.0]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0.88</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L31" t="n">
         <v>0.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N31" t="n">
         <v>0.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0.4</v>
@@ -3112,19 +3112,19 @@
         <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>0.1207819970870288</v>
+        <v>0.4385436849399495</v>
       </c>
       <c r="W31" t="n">
-        <v>0.3451809481865475</v>
+        <v>2.119676014710494</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3171,7 +3171,7 @@
         <v>0.9</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="K32" t="n">
         <v>0.9090909090909091</v>
@@ -3207,10 +3207,10 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.05544078817420241</v>
+        <v>0.09999966178816919</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1718664448392412</v>
+        <v>1.31164857385537</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -3243,11 +3243,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3257,46 +3257,46 @@
         <v>0.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.03184274151731658</v>
+        <v>0.1171292140907579</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1021377035401273</v>
+        <v>1.240624922945283</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -3329,60 +3329,60 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2368083974981233</v>
+        <v>0.000241311481265592</v>
       </c>
       <c r="W34" t="n">
-        <v>0.6260902942051009</v>
+        <v>0.005037504856953613</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -3415,60 +3415,60 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1721486088446183</v>
+        <v>0.100035789431668</v>
       </c>
       <c r="W35" t="n">
-        <v>0.469638360814759</v>
+        <v>1.813017768857535</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -3501,60 +3501,60 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.3971086691007685</v>
+        <v>1.75745875047518e-11</v>
       </c>
       <c r="W36" t="n">
-        <v>1.825158603735911</v>
+        <v>1.325823798115662e-06</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -3587,60 +3587,60 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.3919031043982257</v>
+        <v>0.1470072949078548</v>
       </c>
       <c r="W37" t="n">
-        <v>1.625595760488386</v>
+        <v>0.43942917902641</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -3669,43 +3669,43 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P38" t="n">
         <v>0.2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.8</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3714,19 +3714,19 @@
         <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.3337109196111626</v>
+        <v>0.06525140798257592</v>
       </c>
       <c r="W38" t="n">
-        <v>1.019438307276852</v>
+        <v>0.2196475123590611</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -3755,11 +3755,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3767,52 +3767,52 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="L39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.2</v>
       </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>0.3595531577690493</v>
+        <v>0.1207819970870288</v>
       </c>
       <c r="W39" t="n">
-        <v>8.888630932088095</v>
+        <v>0.3451809481865475</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3853,31 +3853,31 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P40" t="n">
         <v>0.2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3886,19 +3886,19 @@
         <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.3867339947543554</v>
+        <v>0.05544078817420241</v>
       </c>
       <c r="W40" t="n">
-        <v>2.044467752285086</v>
+        <v>0.1718664448392412</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -3927,11 +3927,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3939,37 +3939,37 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6800000000000002</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="L41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>0.2</v>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.8</v>
-      </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -3978,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>0.4000000889113388</v>
+        <v>0.03184274151731658</v>
       </c>
       <c r="W41" t="n">
-        <v>14.41755569293979</v>
+        <v>0.1021377035401273</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -4013,11 +4013,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4028,49 +4028,49 @@
         <v>0.6</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0.3168924722010692</v>
+        <v>0.2368083974981233</v>
       </c>
       <c r="W42" t="n">
-        <v>1.126944466767773</v>
+        <v>0.6260902942051009</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -4099,15 +4099,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -4117,7 +4117,7 @@
         <v>0.5</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K43" t="n">
         <v>0.5454545454545454</v>
@@ -4153,10 +4153,10 @@
         <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0.4058728179093984</v>
+        <v>0.466456094123772</v>
       </c>
       <c r="W43" t="n">
-        <v>1.808043125885058</v>
+        <v>2.48787857038936</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -4185,15 +4185,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4203,7 +4203,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="K44" t="n">
         <v>0.6666666666666666</v>
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>0.274347866061634</v>
+        <v>0.1721486088446183</v>
       </c>
       <c r="W44" t="n">
-        <v>0.8977510327439056</v>
+        <v>0.469638360814759</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -4271,64 +4271,64 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N45" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.2</v>
       </c>
-      <c r="P45" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>0.4528333216910196</v>
+        <v>0.3971086691007685</v>
       </c>
       <c r="W45" t="n">
-        <v>2.353660307895256</v>
+        <v>1.825158603735911</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4375,7 +4375,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="K46" t="n">
         <v>0.6666666666666666</v>
@@ -4411,10 +4411,10 @@
         <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>0.2367654154071854</v>
+        <v>0.3919031043982257</v>
       </c>
       <c r="W46" t="n">
-        <v>0.6436821356944277</v>
+        <v>1.625595760488386</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -4447,60 +4447,60 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0.6</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0.72</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
         <v>4</v>
       </c>
-      <c r="S47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.271347387231235</v>
+        <v>0.3337109196111626</v>
       </c>
       <c r="W47" t="n">
-        <v>0.7593168853963073</v>
+        <v>1.019438307276852</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -4533,39 +4533,39 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="L48" t="n">
         <v>0.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="N48" t="n">
         <v>0.8</v>
       </c>
       <c r="O48" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0.2</v>
@@ -4574,19 +4574,19 @@
         <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>0.3951568556914789</v>
+        <v>0.4138086615202816</v>
       </c>
       <c r="W48" t="n">
-        <v>1.990081634708989</v>
+        <v>1.655538153502472</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -4619,60 +4619,60 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>0.6</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>4</v>
       </c>
-      <c r="S49" t="n">
-        <v>2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1</v>
-      </c>
       <c r="V49" t="n">
-        <v>0.4058183488164996</v>
+        <v>0.3595531577690493</v>
       </c>
       <c r="W49" t="n">
-        <v>2.214745210156345</v>
+        <v>8.888630932088095</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -4696,12 +4696,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -4709,35 +4709,35 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4746,19 +4746,19 @@
         <v>5</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.0001345733862346805</v>
+        <v>0.3867339947543554</v>
       </c>
       <c r="W50" t="n">
-        <v>0.00395144803517134</v>
+        <v>2.044467752285086</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -4795,29 +4795,29 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0.6800000000000002</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -4838,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>3.675374443074839e-05</v>
+        <v>0.4000000889113388</v>
       </c>
       <c r="W51" t="n">
-        <v>0.002315457184602566</v>
+        <v>14.41755569293979</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -4868,69 +4868,69 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
-        <v>0.0007687460226166781</v>
+        <v>0.3168924722010692</v>
       </c>
       <c r="W52" t="n">
-        <v>0.009462578662308666</v>
+        <v>1.126944466767773</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -4954,69 +4954,69 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>9.120370860469717e-07</v>
+        <v>0.2745256712944043</v>
       </c>
       <c r="W53" t="n">
-        <v>0.0005666198825896675</v>
+        <v>0.8164065966441253</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5053,56 +5053,56 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>0.01304433880548594</v>
+        <v>0.4058728179093984</v>
       </c>
       <c r="W54" t="n">
-        <v>0.06850210995139218</v>
+        <v>1.808043125885058</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5139,56 +5139,56 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q55" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0596710921411344</v>
+        <v>0.274347866061634</v>
       </c>
       <c r="W55" t="n">
-        <v>0.1679420708796977</v>
+        <v>0.8977510327439056</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5225,56 +5225,56 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>0.000383766789762362</v>
+        <v>0.4528333216910196</v>
       </c>
       <c r="W56" t="n">
-        <v>0.008955819969676813</v>
+        <v>2.353660307895256</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -5298,69 +5298,69 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>0.001965312259905773</v>
+        <v>0.2367654154071854</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02168084368317157</v>
+        <v>0.6436821356944277</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -5407,46 +5407,46 @@
         <v>0.4</v>
       </c>
       <c r="J58" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O58" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>0.4911803728295393</v>
+        <v>0.5064795486967507</v>
       </c>
       <c r="W58" t="n">
-        <v>2.206318912951169</v>
+        <v>3.197642903981231</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -5470,12 +5470,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5487,25 +5487,25 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L59" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O59" t="n">
         <v>0.4</v>
@@ -5514,10 +5514,10 @@
         <v>0.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
@@ -5526,13 +5526,13 @@
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>0.4893444122439258</v>
+        <v>0.271347387231235</v>
       </c>
       <c r="W59" t="n">
-        <v>2.202226477121664</v>
+        <v>0.7593168853963073</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5573,52 +5573,52 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L60" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N60" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O60" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P60" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>0.3792503956224346</v>
+        <v>0.3951568556914789</v>
       </c>
       <c r="W60" t="n">
-        <v>3.039215938891285</v>
+        <v>1.990081634708989</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[10.0, 14.0]</t>
+          <t>[9.0, 13.0]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5659,52 +5659,52 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P61" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V61" t="n">
-        <v>0.365153924439894</v>
+        <v>0.4058183488164996</v>
       </c>
       <c r="W61" t="n">
-        <v>3.064044758720645</v>
+        <v>2.214745210156345</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5745,31 +5745,31 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6799999999999999</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5778,19 +5778,19 @@
         <v>5</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0.3022528637724701</v>
+        <v>0.0001345733862346805</v>
       </c>
       <c r="W62" t="n">
-        <v>4.017511360044459</v>
+        <v>0.00395144803517134</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5827,35 +5827,35 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7200000000000001</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5864,19 +5864,19 @@
         <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.3207087394940659</v>
+        <v>0.001408877136754058</v>
       </c>
       <c r="W63" t="n">
-        <v>4.207041322968594</v>
+        <v>0.01660173714658113</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -5913,35 +5913,35 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5950,19 +5950,19 @@
         <v>5</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0.2999991617713681</v>
+        <v>3.675374443074839e-05</v>
       </c>
       <c r="W64" t="n">
-        <v>7.990549364687314</v>
+        <v>0.002315457184602566</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5999,35 +5999,35 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -6036,19 +6036,19 @@
         <v>5</v>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.2412384561251016</v>
+        <v>0.0007687460226166781</v>
       </c>
       <c r="W65" t="n">
-        <v>7.311930884758588</v>
+        <v>0.009462578662308666</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -6077,43 +6077,43 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -6122,19 +6122,19 @@
         <v>5</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0.3474995433047675</v>
+        <v>9.120370860469717e-07</v>
       </c>
       <c r="W66" t="n">
-        <v>1.420756012583855</v>
+        <v>0.0005666198825896675</v>
       </c>
       <c r="X66" t="n">
         <v>1000</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -6171,56 +6171,56 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5599999999999999</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.3961238636138605</v>
+        <v>0.01304433880548594</v>
       </c>
       <c r="W67" t="n">
-        <v>2.048727949242881</v>
+        <v>0.06850210995139218</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -6257,56 +6257,56 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
-        <v>0.44</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="L68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
         <v>0.2</v>
       </c>
-      <c r="P68" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>0.4086263936935836</v>
+        <v>0.07513299304102584</v>
       </c>
       <c r="W68" t="n">
-        <v>1.665328687638275</v>
+        <v>0.2154270889426106</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -6343,56 +6343,56 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
-        <v>0.52</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.4045331152687803</v>
+        <v>0.0596710921411344</v>
       </c>
       <c r="W69" t="n">
-        <v>2.234243225486971</v>
+        <v>0.1679420708796977</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -6421,64 +6421,64 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>0.409072277323607</v>
+        <v>0.000383766789762362</v>
       </c>
       <c r="W70" t="n">
-        <v>2.81353688650624</v>
+        <v>0.008955819969676813</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -6507,64 +6507,64 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0.4444444444444445</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>0.4802613670765218</v>
+        <v>0.001965312259905773</v>
       </c>
       <c r="W71" t="n">
-        <v>3.122922144529038</v>
+        <v>0.02168084368317157</v>
       </c>
       <c r="X71" t="n">
         <v>1000</v>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -6601,35 +6601,35 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
-        <v>0.4800000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="L72" t="n">
         <v>0.4</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N72" t="n">
         <v>0.4</v>
       </c>
       <c r="O72" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P72" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q72" t="n">
         <v>0.6</v>
@@ -6638,19 +6638,19 @@
         <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
         <v>3</v>
       </c>
       <c r="V72" t="n">
-        <v>0.4410977749750016</v>
+        <v>0.4911803728295393</v>
       </c>
       <c r="W72" t="n">
-        <v>4.089788073420765</v>
+        <v>2.206318912951169</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -6687,35 +6687,35 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L73" t="n">
         <v>0.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N73" t="n">
         <v>0.6</v>
       </c>
       <c r="O73" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P73" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q73" t="n">
         <v>0.4</v>
@@ -6724,19 +6724,19 @@
         <v>3</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U73" t="n">
         <v>2</v>
       </c>
       <c r="V73" t="n">
-        <v>0.4115567619526363</v>
+        <v>0.4068173238802033</v>
       </c>
       <c r="W73" t="n">
-        <v>4.567419867866478</v>
+        <v>3.023685219118791</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6769,60 +6769,60 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P74" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V74" t="n">
-        <v>0.1006937589725384</v>
+        <v>0.4893444122439258</v>
       </c>
       <c r="W74" t="n">
-        <v>0.9846522764262085</v>
+        <v>2.202226477121664</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6855,60 +6855,60 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O75" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P75" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>0.1000413135005225</v>
+        <v>0.3792503956224346</v>
       </c>
       <c r="W75" t="n">
-        <v>2.419861209590069</v>
+        <v>3.039215938891285</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6941,60 +6941,60 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O76" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V76" t="n">
-        <v>0.100002659029257</v>
+        <v>0.365153924439894</v>
       </c>
       <c r="W76" t="n">
-        <v>1.416974764644635</v>
+        <v>3.064044758720645</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -7031,35 +7031,35 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P77" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -7068,19 +7068,19 @@
         <v>5</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0.1000000000000028</v>
+        <v>0.3022528637724701</v>
       </c>
       <c r="W77" t="n">
-        <v>3.604365355745178</v>
+        <v>4.017511360044459</v>
       </c>
       <c r="X77" t="n">
         <v>1000</v>
@@ -7104,48 +7104,48 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N78" t="n">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -7154,19 +7154,19 @@
         <v>5</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>0.1089648283919164</v>
+        <v>0.3019503184267071</v>
       </c>
       <c r="W78" t="n">
-        <v>0.3599564828622443</v>
+        <v>3.694042890805716</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -7190,16 +7190,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7207,31 +7207,31 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P79" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -7240,19 +7240,19 @@
         <v>5</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0.08700203391764647</v>
+        <v>0.3207087394940659</v>
       </c>
       <c r="W79" t="n">
-        <v>0.2699317603813558</v>
+        <v>4.207041322968594</v>
       </c>
       <c r="X79" t="n">
         <v>1000</v>
@@ -7276,16 +7276,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -7293,31 +7293,31 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="K80" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P80" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -7326,19 +7326,19 @@
         <v>5</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>0.08957444819526278</v>
+        <v>0.2999991617713681</v>
       </c>
       <c r="W80" t="n">
-        <v>0.3088871258012462</v>
+        <v>7.990549364687314</v>
       </c>
       <c r="X80" t="n">
         <v>1000</v>
@@ -7362,16 +7362,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -7379,31 +7379,31 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="P81" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -7412,19 +7412,19 @@
         <v>5</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>0.07025515239509869</v>
+        <v>0.2412384561251016</v>
       </c>
       <c r="W81" t="n">
-        <v>0.2116953797948996</v>
+        <v>7.311930884758588</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -7448,16 +7448,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7465,52 +7465,52 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L82" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N82" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>0.2826566656010984</v>
+        <v>0.3474995433047675</v>
       </c>
       <c r="W82" t="n">
-        <v>0.8516391577351975</v>
+        <v>1.420756012583855</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -7534,69 +7534,69 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="K83" t="n">
-        <v>0.6</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="N83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P83" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>0.267710400875674</v>
+        <v>0.284456417954159</v>
       </c>
       <c r="W83" t="n">
-        <v>0.7719604573305074</v>
+        <v>1.170412372416286</v>
       </c>
       <c r="X83" t="n">
         <v>1000</v>
@@ -7620,20 +7620,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7643,7 +7643,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="K84" t="n">
         <v>0.6666666666666666</v>
@@ -7679,10 +7679,10 @@
         <v>1</v>
       </c>
       <c r="V84" t="n">
-        <v>0.3236988432962713</v>
+        <v>0.3961238636138605</v>
       </c>
       <c r="W84" t="n">
-        <v>1.059829178831371</v>
+        <v>2.048727949242881</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -7706,69 +7706,69 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>csp_before_split</t>
+          <t>split_before_csp</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
-        <v>0.7200000000000002</v>
+        <v>0.44</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L85" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N85" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O85" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P85" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R85" t="n">
+        <v>3</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
         <v>4</v>
       </c>
-      <c r="S85" t="n">
-        <v>2</v>
-      </c>
-      <c r="T85" t="n">
-        <v>3</v>
-      </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>0.2733082408344384</v>
+        <v>0.4086263936935836</v>
       </c>
       <c r="W85" t="n">
-        <v>1.037607625706844</v>
+        <v>1.665328687638275</v>
       </c>
       <c r="X85" t="n">
         <v>1000</v>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7801,60 +7801,60 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>0.3207550891298906</v>
+        <v>0.4045331152687803</v>
       </c>
       <c r="W86" t="n">
-        <v>1.620387803974908</v>
+        <v>2.234243225486971</v>
       </c>
       <c r="X86" t="n">
         <v>1000</v>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7887,39 +7887,39 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="K87" t="n">
-        <v>0.7499999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L87" t="n">
         <v>0.6</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N87" t="n">
         <v>0.6</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q87" t="n">
         <v>0.4</v>
@@ -7928,19 +7928,19 @@
         <v>3</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>0.210659745724957</v>
+        <v>0.409072277323607</v>
       </c>
       <c r="W87" t="n">
-        <v>1.476325356961137</v>
+        <v>2.81353688650624</v>
       </c>
       <c r="X87" t="n">
         <v>1000</v>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7973,39 +7973,39 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.3600000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L88" t="n">
         <v>0.4</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N88" t="n">
         <v>0.4</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>0.6</v>
@@ -8014,19 +8014,19 @@
         <v>2</v>
       </c>
       <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
         <v>5</v>
       </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
       <c r="U88" t="n">
         <v>3</v>
       </c>
       <c r="V88" t="n">
-        <v>0.2997961340871695</v>
+        <v>0.5418698366436101</v>
       </c>
       <c r="W88" t="n">
-        <v>1.620573552706804</v>
+        <v>3.361476546862324</v>
       </c>
       <c r="X88" t="n">
         <v>1000</v>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8059,60 +8059,60 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="K89" t="n">
-        <v>0.7499999999999999</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="L89" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V89" t="n">
-        <v>0.2135337564910305</v>
+        <v>0.4802613670765218</v>
       </c>
       <c r="W89" t="n">
-        <v>1.450647983052666</v>
+        <v>3.122922144529038</v>
       </c>
       <c r="X89" t="n">
         <v>1000</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8145,60 +8145,60 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O90" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P90" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V90" t="n">
-        <v>0.141361632809413</v>
+        <v>0.4410977749750016</v>
       </c>
       <c r="W90" t="n">
-        <v>0.4599944149030824</v>
+        <v>4.089788073420765</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[8.0, 15.0]</t>
+          <t>[10.0, 14.0]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8231,33 +8231,33 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.6</v>
       </c>
       <c r="L91" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M91" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O91" t="n">
         <v>0.6</v>
@@ -8266,10 +8266,10 @@
         <v>0.4</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -8278,13 +8278,13 @@
         <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V91" t="n">
-        <v>0.2228591474551971</v>
+        <v>0.4115567619526363</v>
       </c>
       <c r="W91" t="n">
-        <v>0.7413221213189098</v>
+        <v>4.567419867866478</v>
       </c>
       <c r="X91" t="n">
         <v>1000</v>
@@ -8313,43 +8313,43 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -8358,19 +8358,19 @@
         <v>5</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>0.0654382870531162</v>
+        <v>0.1006937589725384</v>
       </c>
       <c r="W92" t="n">
-        <v>0.233149431281837</v>
+        <v>0.9846522764262085</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -8399,64 +8399,64 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
-        <v>0.92</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L93" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N93" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P93" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
+        <v>5</v>
+      </c>
+      <c r="S93" t="n">
         <v>4</v>
       </c>
-      <c r="S93" t="n">
-        <v>3</v>
-      </c>
       <c r="T93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0.1958598994841339</v>
+        <v>0.1000543068329615</v>
       </c>
       <c r="W93" t="n">
-        <v>0.5364504527856676</v>
+        <v>1.498460756424054</v>
       </c>
       <c r="X93" t="n">
         <v>1000</v>
@@ -8485,64 +8485,64 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4400000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L94" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N94" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P94" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>0.398927057626734</v>
+        <v>0.1000413135005225</v>
       </c>
       <c r="W94" t="n">
-        <v>1.445955484550971</v>
+        <v>2.419861209590069</v>
       </c>
       <c r="X94" t="n">
         <v>1000</v>
@@ -8571,64 +8571,64 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
-        <v>0.52</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L95" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N95" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0.3740761767790796</v>
+        <v>0.100002659029257</v>
       </c>
       <c r="W95" t="n">
-        <v>1.409664417488775</v>
+        <v>1.416974764644635</v>
       </c>
       <c r="X95" t="n">
         <v>1000</v>
@@ -8657,64 +8657,64 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>split_before_csp</t>
+          <t>csp_before_split</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4800000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N96" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P96" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
+        <v>5</v>
+      </c>
+      <c r="S96" t="n">
         <v>4</v>
       </c>
-      <c r="S96" t="n">
-        <v>2</v>
-      </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>0.3678561810624719</v>
+        <v>0.1000000000000028</v>
       </c>
       <c r="W96" t="n">
-        <v>1.648684332496458</v>
+        <v>3.604365355745178</v>
       </c>
       <c r="X96" t="n">
         <v>1000</v>
@@ -8743,66 +8743,2130 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>5</v>
+      </c>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0.1089648283919164</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0.3599564828622443</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0.126698386393799</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0.4137099283167055</v>
+      </c>
+      <c r="X98" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0.08700203391764647</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.2699317603813558</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>5</v>
+      </c>
+      <c r="S100" t="n">
+        <v>4</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0.08957444819526278</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0.3088871258012462</v>
+      </c>
+      <c r="X100" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>5</v>
+      </c>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0.07025515239509869</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0.2116953797948996</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R102" t="n">
+        <v>3</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" t="n">
+        <v>3</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0.2826566656010984</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0.8516391577351975</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R103" t="n">
+        <v>3</v>
+      </c>
+      <c r="S103" t="n">
+        <v>2</v>
+      </c>
+      <c r="T103" t="n">
+        <v>3</v>
+      </c>
+      <c r="U103" t="n">
+        <v>2</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0.3704700086403441</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1.548055943306007</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R104" t="n">
+        <v>3</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3</v>
+      </c>
+      <c r="T104" t="n">
+        <v>2</v>
+      </c>
+      <c r="U104" t="n">
+        <v>2</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.267710400875674</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0.7719604573305074</v>
+      </c>
+      <c r="X104" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R105" t="n">
+        <v>4</v>
+      </c>
+      <c r="S105" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" t="n">
+        <v>3</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0.3236988432962713</v>
+      </c>
+      <c r="W105" t="n">
+        <v>1.059829178831371</v>
+      </c>
+      <c r="X105" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>csp_before_split</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R106" t="n">
+        <v>4</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="n">
+        <v>3</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0.2733082408344384</v>
+      </c>
+      <c r="W106" t="n">
+        <v>1.037607625706844</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>split_before_csp</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>3</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>4</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0.3207550891298906</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1.620387803974908</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R108" t="n">
+        <v>2</v>
+      </c>
+      <c r="S108" t="n">
+        <v>4</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>3</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0.2937341439740613</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0.7949598536541619</v>
+      </c>
+      <c r="X108" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R109" t="n">
+        <v>3</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>2</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0.210659745724957</v>
+      </c>
+      <c r="W109" t="n">
+        <v>1.476325356961137</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>3</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0.2997961340871695</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1.620573552706804</v>
+      </c>
+      <c r="X110" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>(0, 1, -2, -1)</t>
         </is>
       </c>
-      <c r="H97" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I97" t="n">
+      <c r="H111" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>2</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0.2135337564910305</v>
+      </c>
+      <c r="W111" t="n">
+        <v>1.450647983052666</v>
+      </c>
+      <c r="X111" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>5</v>
+      </c>
+      <c r="S112" t="n">
+        <v>4</v>
+      </c>
+      <c r="T112" t="n">
+        <v>1</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0.141361632809413</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0.4599944149030824</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>5</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0.07076396499747113</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0.2574292639929415</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R114" t="n">
+        <v>4</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3</v>
+      </c>
+      <c r="T114" t="n">
+        <v>2</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0.2228591474551971</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0.7413221213189098</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>5</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0.0654382870531162</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0.233149431281837</v>
+      </c>
+      <c r="X115" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3</v>
+      </c>
+      <c r="T116" t="n">
+        <v>2</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0.1958598994841339</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0.5364504527856676</v>
+      </c>
+      <c r="X116" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3</v>
+      </c>
+      <c r="S117" t="n">
+        <v>2</v>
+      </c>
+      <c r="T117" t="n">
+        <v>3</v>
+      </c>
+      <c r="U117" t="n">
+        <v>2</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.398927057626734</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.445955484550971</v>
+      </c>
+      <c r="X117" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R118" t="n">
+        <v>3</v>
+      </c>
+      <c r="S118" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" t="n">
+        <v>3</v>
+      </c>
+      <c r="U118" t="n">
+        <v>2</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4195505577427783</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.970526133359259</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>3</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" t="n">
+        <v>3</v>
+      </c>
+      <c r="U119" t="n">
+        <v>2</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3740761767790796</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1.409664417488775</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I120" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J120" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>4</v>
+      </c>
+      <c r="S120" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" t="n">
+        <v>3</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3678561810624719</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.648684332496458</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>05_08 Artem</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>01_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[8.0, 15.0]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>split_before_csp</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="J121" t="n">
         <v>0.52</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K121" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="L97" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M97" t="n">
+      <c r="L121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M121" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N97" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q97" t="n">
+      <c r="N121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q121" t="n">
         <v>0.2</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R121" t="n">
         <v>4</v>
       </c>
-      <c r="S97" t="n">
-        <v>2</v>
-      </c>
-      <c r="T97" t="n">
-        <v>3</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" t="n">
+      <c r="S121" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" t="n">
+        <v>3</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
         <v>0.3394020323892886</v>
       </c>
-      <c r="W97" t="n">
+      <c r="W121" t="n">
         <v>1.544906808733981</v>
       </c>
-      <c r="X97" t="n">
+      <c r="X121" t="n">
         <v>1000</v>
       </c>
     </row>
